--- a/minute_filler/templates/Invoice Template.xlsx
+++ b/minute_filler/templates/Invoice Template.xlsx
@@ -35,7 +35,8 @@
     <definedName name="EmailCopies">Setup!$B$22</definedName>
     <definedName name="Indexes">Setup!$B$23</definedName>
     <definedName name="IndexFrom">Setup!$B$24</definedName>
-    <definedName name="Turnaround">Setup!$A$27:$B$30</definedName>
+    <definedName name="IndexEach">Setup!$B$25</definedName>
+    <definedName name="Turnaround">Setup!$A$28:$B$31</definedName>
     <definedName name="RateTable">Rates!$A$2:$E$5</definedName>
     <definedName name="InvoiceNo">Job!$B$2</definedName>
     <definedName name="InvoiceDate">Job!$B$3</definedName>
@@ -558,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -785,7 +786,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Index for each party + judge</t>
+          <t>Index + judge's index</t>
         </is>
       </c>
       <c r="B23" s="3" t="b">
@@ -803,59 +804,69 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Index for each party (FALSE: one, split)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>TURNAROUND WORDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Immediate</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Delivered at the time of trial.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Immediate</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>1 business day from receipt of payment.</t>
+          <t>Delivered at the time of trial.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Expedite</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>1 week from receipt of payment.</t>
+          <t>1 business day from receipt of payment.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>Expedite</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>1 week from receipt of payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>2-4 weeks from receipt of payment.</t>
         </is>
@@ -863,7 +874,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B19 B20 B21 B22 B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B19 B20 B21 B22 B23 B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1316,7 +1327,7 @@
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>Indexes</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
@@ -1375,7 +1386,7 @@
         <v/>
       </c>
       <c r="I2" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E2*Parties,0)</f>
+        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E2*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J2" s="10">
@@ -1387,7 +1398,7 @@
         <v/>
       </c>
       <c r="L2" s="10">
-        <f>ROUND(K2/Parties,2)</f>
+        <f>ROUNDUP(ROUND(K2/Parties,6),2)</f>
         <v/>
       </c>
       <c r="M2" s="10">
@@ -1430,7 +1441,7 @@
         <v/>
       </c>
       <c r="I3" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E3*Parties,0)</f>
+        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E3*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J3" s="10">
@@ -1442,7 +1453,7 @@
         <v/>
       </c>
       <c r="L3" s="10">
-        <f>ROUND(K3/Parties,2)</f>
+        <f>ROUNDUP(ROUND(K3/Parties,6),2)</f>
         <v/>
       </c>
       <c r="M3" s="10">
@@ -1485,7 +1496,7 @@
         <v/>
       </c>
       <c r="I4" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E4*Parties,0)</f>
+        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E4*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J4" s="10">
@@ -1497,7 +1508,7 @@
         <v/>
       </c>
       <c r="L4" s="10">
-        <f>ROUND(K4/Parties,2)</f>
+        <f>ROUNDUP(ROUND(K4/Parties,6),2)</f>
         <v/>
       </c>
       <c r="M4" s="10">
@@ -1540,7 +1551,7 @@
         <v/>
       </c>
       <c r="I5" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E5*Parties,0)</f>
+        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E5*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J5" s="10">
@@ -1552,7 +1563,7 @@
         <v/>
       </c>
       <c r="L5" s="10">
-        <f>ROUND(K5/Parties,2)</f>
+        <f>ROUNDUP(ROUND(K5/Parties,6),2)</f>
         <v/>
       </c>
       <c r="M5" s="10">
@@ -1563,7 +1574,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Each party pays one share of the original plus their own copy (and e-mailed copy and index).</t>
+          <t>Each party pays one share of the original, the index and the judge's index (the index in full when Setup says each party gets one), plus their own copy and e-mailed copy, rounded up to the cent. Every party orders every page.</t>
         </is>
       </c>
     </row>

--- a/minute_filler/templates/Invoice Template.xlsx
+++ b/minute_filler/templates/Invoice Template.xlsx
@@ -43,17 +43,18 @@
     <definedName name="Pages">Job!$B$4</definedName>
     <definedName name="Parties">Job!$B$5</definedName>
     <definedName name="Speed">Job!$B$6</definedName>
-    <definedName name="CaseTitle">Job!$B$9</definedName>
-    <definedName name="IndexNo">Job!$B$10</definedName>
-    <definedName name="CaseDates">Job!$B$11</definedName>
-    <definedName name="Judge">Job!$B$12</definedName>
-    <definedName name="Part">Job!$B$13</definedName>
-    <definedName name="Court">Job!$B$14</definedName>
-    <definedName name="BillName">Job!$B$17</definedName>
-    <definedName name="BillFirm">Job!$B$18</definedName>
-    <definedName name="BillAddress1">Job!$B$19</definedName>
-    <definedName name="BillAddress2">Job!$B$20</definedName>
-    <definedName name="BillEmail">Job!$B$21</definedName>
+    <definedName name="TranscriptPages">Job!$B$7</definedName>
+    <definedName name="CaseTitle">Job!$B$10</definedName>
+    <definedName name="IndexNo">Job!$B$11</definedName>
+    <definedName name="CaseDates">Job!$B$12</definedName>
+    <definedName name="Judge">Job!$B$13</definedName>
+    <definedName name="Part">Job!$B$14</definedName>
+    <definedName name="Court">Job!$B$15</definedName>
+    <definedName name="BillName">Job!$B$18</definedName>
+    <definedName name="BillFirm">Job!$B$19</definedName>
+    <definedName name="BillAddress1">Job!$B$20</definedName>
+    <definedName name="BillAddress2">Job!$B$21</definedName>
+    <definedName name="BillEmail">Job!$B$22</definedName>
     <definedName name="CalcSpeeds">Calculation!$A$2:$A$5</definedName>
     <definedName name="CalcEach">Calculation!$L$2:$L$5</definedName>
     <definedName name="CalcPerPage">Calculation!$M$2:$M$5</definedName>
@@ -810,7 +811,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -950,13 +951,13 @@
         <v>6.5</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="4">
@@ -1020,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1090,154 +1091,162 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Whole transcript's pages (blank: Pages)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>CASE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Smith v. Jones</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Index No.</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>712222/2024</t>
+          <t>Smith v. Jones</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Date(s) of proceedings</t>
+          <t>Index No.</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>5/22/2026</t>
+          <t>712222/2024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Date(s) of proceedings</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hon. A. Example</t>
+          <t>5/22/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Part</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>Hon. A. Example</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Court</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Supreme Court, Example County</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>BILL TO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Attorney</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Alex Example, Esq.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Firm</t>
+          <t>Attorney</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Example Firm LLP</t>
+          <t>Alex Example, Esq.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Firm</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>1 Main Street</t>
+          <t>Example Firm LLP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>City, state, ZIP</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Anytown, NY 10000</t>
+          <t>1 Main Street</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>City, state, ZIP</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Anytown, NY 10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>billing@examplefirm.com</t>
         </is>
@@ -1386,7 +1395,7 @@
         <v/>
       </c>
       <c r="I2" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E2*IF(IndexEach,Parties,1),0)</f>
+        <f>IF(AND(Indexes,MAX(Pages,N(TranscriptPages))&gt;=IndexFrom),Pages*E2*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J2" s="10">
@@ -1441,7 +1450,7 @@
         <v/>
       </c>
       <c r="I3" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E3*IF(IndexEach,Parties,1),0)</f>
+        <f>IF(AND(Indexes,MAX(Pages,N(TranscriptPages))&gt;=IndexFrom),Pages*E3*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J3" s="10">
@@ -1496,7 +1505,7 @@
         <v/>
       </c>
       <c r="I4" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E4*IF(IndexEach,Parties,1),0)</f>
+        <f>IF(AND(Indexes,MAX(Pages,N(TranscriptPages))&gt;=IndexFrom),Pages*E4*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J4" s="10">
@@ -1551,7 +1560,7 @@
         <v/>
       </c>
       <c r="I5" s="10">
-        <f>IF(AND(Indexes,Pages&gt;=IndexFrom),Pages*E5*IF(IndexEach,Parties,1),0)</f>
+        <f>IF(AND(Indexes,MAX(Pages,N(TranscriptPages))&gt;=IndexFrom),Pages*E5*IF(IndexEach,Parties,1),0)</f>
         <v/>
       </c>
       <c r="J5" s="10">
@@ -1574,7 +1583,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Each party pays one share of the original, the index and the judge's index (the index in full when Setup says each party gets one), plus their own copy and e-mailed copy, rounded up to the cent. Every party orders every page.</t>
+          <t>Each party pays one share of the original and the judge's index, plus its own copy, e-mailed copy and index (one share of a single index when Setup's IndexEach is FALSE), rounded up to the cent. Every party orders every page. The index comes once the whole transcript (Job: every reporter's pages) has Setup's number of pages; it is charged on your Pages.</t>
         </is>
       </c>
     </row>
